--- a/02_Zero_Shot/outputs/Embedding/all-mpnet-base-v2/RESULT_f-droid_all-mpnet-base-v2_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/all-mpnet-base-v2/RESULT_f-droid_all-mpnet-base-v2_zeroshot.xlsx
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.535039234000124</v>
+        <v>40.57866872700106</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003356226411122887</v>
+        <v>0.01428323432840586</v>
       </c>
     </row>
   </sheetData>
